--- a/data/trans_dic/P6904-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,85; 79,35</t>
+          <t>50,54; 79,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,61; 74,29</t>
+          <t>40,42; 74,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,49; 54,52</t>
+          <t>28,31; 54,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,5; 78,04</t>
+          <t>34,11; 77,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,96; 72,49</t>
+          <t>34,21; 73,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,43; 82,36</t>
+          <t>45,84; 82,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,14; 82,38</t>
+          <t>52,75; 81,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,68; 95,41</t>
+          <t>53,94; 96,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,91; 72,79</t>
+          <t>48,35; 72,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,49; 72,87</t>
+          <t>49,45; 73,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,09; 62,72</t>
+          <t>42,42; 62,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,01; 81,63</t>
+          <t>52,5; 81,56</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,95; 62,87</t>
+          <t>38,01; 63,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,35; 77,78</t>
+          <t>51,34; 77,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,79; 83,66</t>
+          <t>64,45; 83,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37,54; 75,33</t>
+          <t>39,52; 76,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,56; 76,36</t>
+          <t>41,84; 74,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 57,74</t>
+          <t>22,81; 57,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,85; 90,15</t>
+          <t>63,33; 89,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,79; 66,3</t>
+          <t>39,57; 65,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,17; 62,32</t>
+          <t>42,84; 62,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,21; 65,3</t>
+          <t>43,61; 65,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67,67; 83,28</t>
+          <t>67,95; 83,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,42; 65,85</t>
+          <t>43,82; 66,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,69; 70,25</t>
+          <t>37,3; 70,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,76; 77,63</t>
+          <t>38,69; 77,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,33; 95,68</t>
+          <t>63,58; 95,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,87; 65,35</t>
+          <t>37,36; 64,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,3; 63,46</t>
+          <t>22,25; 63,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,56; 72,4</t>
+          <t>22,42; 70,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,76; 86,59</t>
+          <t>32,04; 86,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,99; 68,05</t>
+          <t>43,95; 68,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,6; 61,51</t>
+          <t>35,94; 62,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,96; 69,51</t>
+          <t>39,58; 69,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,36; 88,99</t>
+          <t>59,01; 87,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,35; 62,67</t>
+          <t>44,61; 62,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,16; 54,94</t>
+          <t>29,93; 55,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,09; 64,74</t>
+          <t>35,64; 67,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,48; 83,24</t>
+          <t>49,81; 82,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54,9; 89,37</t>
+          <t>58,87; 89,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,39; 62,61</t>
+          <t>22,8; 62,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,11; 69,45</t>
+          <t>34,72; 70,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,15; 80,82</t>
+          <t>45,32; 81,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75,32; 96,91</t>
+          <t>75,58; 96,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,07; 54,08</t>
+          <t>31,31; 53,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,21; 62,87</t>
+          <t>39,75; 64,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,56; 78,47</t>
+          <t>54,74; 78,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,48; 93,76</t>
+          <t>73,26; 93,72</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,31; 61,75</t>
+          <t>19,68; 60,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,77; 100,0</t>
+          <t>64,98; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,78; 83,49</t>
+          <t>29,76; 83,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,07; 67,12</t>
+          <t>27,96; 66,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,82</t>
+          <t>0,0; 57,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,78; 91,93</t>
+          <t>30,36; 91,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,75; 100,0</t>
+          <t>32,16; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,55; 65,41</t>
+          <t>27,49; 66,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,81; 50,84</t>
+          <t>17,78; 52,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,89; 92,57</t>
+          <t>58,82; 91,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,5; 84,86</t>
+          <t>41,45; 85,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,28; 60,33</t>
+          <t>32,28; 61,15</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,17; 54,8</t>
+          <t>25,18; 56,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,01; 70,62</t>
+          <t>40,3; 70,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,84; 55,23</t>
+          <t>17,03; 57,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46,46; 76,38</t>
+          <t>44,72; 76,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,44; 70,42</t>
+          <t>19,7; 70,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,38; 51,67</t>
+          <t>6,5; 52,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,98; 100,0</t>
+          <t>44,35; 100,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,21; 71,9</t>
+          <t>41,77; 71,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,53; 53,82</t>
+          <t>29,55; 54,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36,24; 61,68</t>
+          <t>36,79; 62,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,98; 66,67</t>
+          <t>30,36; 66,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>48,02; 69,78</t>
+          <t>47,86; 69,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,61; 59,94</t>
+          <t>37,39; 59,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,32; 54,45</t>
+          <t>27,13; 55,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54,26; 76,14</t>
+          <t>53,65; 76,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,78; 68,07</t>
+          <t>44,71; 67,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,09; 66,96</t>
+          <t>37,85; 67,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,14; 72,32</t>
+          <t>41,67; 71,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,75; 73,01</t>
+          <t>44,9; 72,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,55; 74,77</t>
+          <t>55,19; 75,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,21; 58,76</t>
+          <t>41,81; 59,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39,24; 59,77</t>
+          <t>38,42; 58,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53,97; 70,9</t>
+          <t>54,43; 71,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,69; 69,02</t>
+          <t>52,5; 68,98</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>53,18; 71,86</t>
+          <t>53,28; 70,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,73; 56,31</t>
+          <t>27,55; 56,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,17; 53,77</t>
+          <t>22,71; 54,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62,98; 85,58</t>
+          <t>63,2; 85,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,41; 76,39</t>
+          <t>50,28; 76,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,85; 75,1</t>
+          <t>36,42; 73,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,0; 73,4</t>
+          <t>30,09; 75,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,52; 69,96</t>
+          <t>40,4; 69,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>55,56; 70,5</t>
+          <t>54,68; 70,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36,36; 59,57</t>
+          <t>35,42; 59,63</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30,07; 56,9</t>
+          <t>30,59; 56,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,2; 73,14</t>
+          <t>55,42; 72,86</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47,36; 56,78</t>
+          <t>47,09; 56,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49,21; 60,81</t>
+          <t>49,14; 60,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54,1; 64,93</t>
+          <t>54,09; 65,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55,63; 67,07</t>
+          <t>55,66; 66,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,5; 59,0</t>
+          <t>44,96; 58,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,37; 58,36</t>
+          <t>44,95; 58,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,83; 73,65</t>
+          <t>60,93; 73,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>59,44; 75,25</t>
+          <t>59,7; 75,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48,19; 55,86</t>
+          <t>48,28; 55,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49,01; 58,03</t>
+          <t>49,26; 58,71</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58,35; 66,58</t>
+          <t>58,47; 66,71</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>59,07; 69,2</t>
+          <t>59,13; 68,85</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21787; 33995</t>
+          <t>21655; 33892</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16829; 29342</t>
+          <t>15963; 29375</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16105; 31937</t>
+          <t>16585; 31667</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8303; 18782</t>
+          <t>8210; 18677</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10005; 20744</t>
+          <t>9791; 20979</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12712; 23043</t>
+          <t>12825; 23115</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22135; 33679</t>
+          <t>21567; 33437</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8615; 15032</t>
+          <t>8498; 15165</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34949; 52017</t>
+          <t>34555; 51560</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32714; 49164</t>
+          <t>33363; 49346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41859; 62384</t>
+          <t>42192; 62099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20714; 32509</t>
+          <t>20906; 32480</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27475; 45514</t>
+          <t>27520; 46139</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29057; 44016</t>
+          <t>29053; 44022</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53634; 69256</t>
+          <t>53355; 69119</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17373; 34861</t>
+          <t>18291; 35173</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13912; 24960</t>
+          <t>13678; 24314</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7925; 19813</t>
+          <t>7827; 19757</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27261; 38493</t>
+          <t>27038; 38054</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18084; 30130</t>
+          <t>17984; 29902</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43267; 65485</t>
+          <t>45020; 65942</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39280; 59361</t>
+          <t>39647; 59087</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84916; 104504</t>
+          <t>85263; 105120</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39830; 60396</t>
+          <t>40196; 61072</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13435; 25723</t>
+          <t>13659; 25814</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10566; 19645</t>
+          <t>9790; 19507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13673; 20335</t>
+          <t>13513; 20319</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18746; 32343</t>
+          <t>18491; 31810</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4844; 13786</t>
+          <t>4834; 13734</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4047; 12984</t>
+          <t>4022; 12565</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4470; 10825</t>
+          <t>4005; 10788</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19744; 31251</t>
+          <t>20182; 31252</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20771; 35882</t>
+          <t>20965; 36253</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16846; 30057</t>
+          <t>17115; 30226</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20037; 30039</t>
+          <t>19920; 29559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42321; 59801</t>
+          <t>42571; 59358</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17007; 32043</t>
+          <t>17455; 32603</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14843; 29041</t>
+          <t>15989; 30373</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16712; 27025</t>
+          <t>16171; 26752</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22152; 36065</t>
+          <t>23758; 36061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5085; 14216</t>
+          <t>5176; 14268</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9482; 20512</t>
+          <t>10253; 20859</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13515; 24194</t>
+          <t>13567; 24402</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60747; 78158</t>
+          <t>60957; 77496</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24364; 43821</t>
+          <t>25371; 43034</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29172; 46770</t>
+          <t>29573; 47787</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34046; 48967</t>
+          <t>34155; 48947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88910; 113456</t>
+          <t>88646; 113407</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4661; 14174</t>
+          <t>4518; 13860</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10310; 16169</t>
+          <t>10507; 16169</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4131; 12416</t>
+          <t>4425; 12353</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4807; 11919</t>
+          <t>4966; 11855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4936</t>
+          <t>0; 4005</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3589; 10720</t>
+          <t>3540; 10723</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1948; 5771</t>
+          <t>1856; 5771</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2807; 7186</t>
+          <t>3020; 7273</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5330; 15215</t>
+          <t>5322; 15629</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16390; 25762</t>
+          <t>16370; 25399</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8566; 17516</t>
+          <t>8556; 17617</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8991; 17339</t>
+          <t>9279; 17576</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10106; 22912</t>
+          <t>10526; 23692</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17355; 30636</t>
+          <t>17483; 30530</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4001; 12391</t>
+          <t>3820; 12865</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14688; 24148</t>
+          <t>14138; 24040</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2036; 9924</t>
+          <t>2776; 9889</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>968; 7845</t>
+          <t>986; 8000</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3266; 7427</t>
+          <t>3294; 7427</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12754; 21726</t>
+          <t>12622; 21534</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15393; 30089</t>
+          <t>16519; 30343</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21226; 36120</t>
+          <t>21548; 36881</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8953; 19907</t>
+          <t>9066; 19780</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29689; 43147</t>
+          <t>29593; 43206</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34153; 53015</t>
+          <t>33071; 52900</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14085; 29135</t>
+          <t>14518; 29822</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42506; 59652</t>
+          <t>42028; 59941</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32771; 49811</t>
+          <t>32718; 49725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15713; 29152</t>
+          <t>16480; 29433</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19545; 33543</t>
+          <t>19327; 33012</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24917; 40656</t>
+          <t>25001; 40516</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>38471; 52734</t>
+          <t>38920; 53239</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>55711; 77554</t>
+          <t>55180; 78108</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39197; 59701</t>
+          <t>38377; 58084</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72327; 95027</t>
+          <t>72954; 96196</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>75720; 99187</t>
+          <t>75440; 99126</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>57921; 78266</t>
+          <t>58026; 77224</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12797; 25985</t>
+          <t>12713; 26106</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9098; 21116</t>
+          <t>8921; 21411</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35745; 48575</t>
+          <t>35869; 48708</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>23602; 38029</t>
+          <t>25031; 38223</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10997; 23035</t>
+          <t>11171; 22568</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6420; 15707</t>
+          <t>6439; 16160</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>22168; 38274</t>
+          <t>22102; 37906</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>88179; 111889</t>
+          <t>86779; 111576</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27932; 45759</t>
+          <t>27213; 45807</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18245; 34521</t>
+          <t>18558; 34482</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>61528; 81531</t>
+          <t>61778; 81212</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>223693; 268198</t>
+          <t>222390; 267606</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>160143; 197915</t>
+          <t>159921; 196372</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>189336; 227259</t>
+          <t>189315; 228223</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>188867; 227692</t>
+          <t>188962; 227403</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>100160; 129872</t>
+          <t>98975; 128347</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94801; 124703</t>
+          <t>96046; 125458</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>131567; 159313</t>
+          <t>131790; 158949</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>210530; 266559</t>
+          <t>211471; 267993</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>333659; 386773</t>
+          <t>334291; 387206</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>264194; 312849</t>
+          <t>265561; 316514</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>330461; 377016</t>
+          <t>331123; 377794</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>409751; 480048</t>
+          <t>410195; 477653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6904-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,54; 79,11</t>
+          <t>52,03; 81,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,42; 74,38</t>
+          <t>41,76; 73,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,31; 54,06</t>
+          <t>25,57; 54,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,11; 77,6</t>
+          <t>47,09; 81,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,21; 73,3</t>
+          <t>31,39; 71,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,84; 82,62</t>
+          <t>44,42; 82,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,75; 81,78</t>
+          <t>53,27; 82,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,94; 96,26</t>
+          <t>56,99; 92,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>48,35; 72,15</t>
+          <t>47,76; 72,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,45; 73,14</t>
+          <t>47,23; 72,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,42; 62,44</t>
+          <t>43,03; 63,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,5; 81,56</t>
+          <t>56,54; 82,87</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,01; 63,73</t>
+          <t>36,29; 62,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,34; 77,79</t>
+          <t>51,06; 76,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,45; 83,49</t>
+          <t>65,2; 83,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,52; 76,0</t>
+          <t>40,62; 75,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,84; 74,38</t>
+          <t>39,36; 74,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,81; 57,57</t>
+          <t>23,54; 57,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,33; 89,13</t>
+          <t>64,1; 90,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,57; 65,8</t>
+          <t>40,05; 65,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42,84; 62,75</t>
+          <t>41,83; 63,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,61; 65,0</t>
+          <t>43,29; 65,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67,95; 83,77</t>
+          <t>68,26; 83,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,82; 66,58</t>
+          <t>45,01; 66,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,3; 70,5</t>
+          <t>37,62; 69,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,69; 77,09</t>
+          <t>42,59; 80,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,58; 95,6</t>
+          <t>62,69; 95,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,36; 64,27</t>
+          <t>37,85; 63,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,25; 63,22</t>
+          <t>22,35; 63,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,42; 70,06</t>
+          <t>21,39; 70,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,04; 86,29</t>
+          <t>31,95; 86,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,95; 68,05</t>
+          <t>43,36; 66,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,94; 62,14</t>
+          <t>36,94; 61,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,58; 69,9</t>
+          <t>40,69; 70,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,01; 87,57</t>
+          <t>60,2; 87,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,61; 62,21</t>
+          <t>44,85; 62,4</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>76,89%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,93; 55,9</t>
+          <t>28,74; 54,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,64; 67,71</t>
+          <t>35,2; 66,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,81; 82,4</t>
+          <t>49,26; 83,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,87; 89,36</t>
+          <t>55,0; 87,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 62,84</t>
+          <t>22,18; 63,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,72; 70,62</t>
+          <t>34,8; 70,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,32; 81,52</t>
+          <t>46,82; 81,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75,58; 96,09</t>
+          <t>68,32; 88,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,31; 53,11</t>
+          <t>30,05; 53,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,75; 64,23</t>
+          <t>40,16; 62,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,74; 78,44</t>
+          <t>55,4; 78,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,26; 93,72</t>
+          <t>67,27; 85,15</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,68; 60,38</t>
+          <t>19,16; 61,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,98; 100,0</t>
+          <t>63,09; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,76; 83,08</t>
+          <t>28,13; 83,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,96; 66,76</t>
+          <t>29,55; 67,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,46</t>
+          <t>0,0; 57,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,36; 91,96</t>
+          <t>31,74; 91,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,16; 100,0</t>
+          <t>33,67; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,49; 66,21</t>
+          <t>26,82; 63,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,78; 52,23</t>
+          <t>19,13; 52,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,82; 91,27</t>
+          <t>58,94; 90,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41,45; 85,35</t>
+          <t>39,08; 84,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,28; 61,15</t>
+          <t>33,25; 62,02</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,18; 56,67</t>
+          <t>25,15; 56,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,3; 70,38</t>
+          <t>40,45; 70,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,03; 57,34</t>
+          <t>17,67; 58,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44,72; 76,04</t>
+          <t>48,21; 77,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,7; 70,16</t>
+          <t>19,07; 70,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 52,69</t>
+          <t>6,43; 47,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,35; 100,0</t>
+          <t>57,79; 100,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,77; 71,27</t>
+          <t>42,55; 70,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,55; 54,28</t>
+          <t>28,56; 55,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36,79; 62,98</t>
+          <t>36,72; 62,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30,36; 66,24</t>
+          <t>30,93; 67,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47,86; 69,88</t>
+          <t>49,6; 70,76</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,39; 59,81</t>
+          <t>38,44; 61,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,13; 55,73</t>
+          <t>27,52; 55,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,65; 76,51</t>
+          <t>54,08; 76,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,71; 67,95</t>
+          <t>46,8; 70,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,85; 67,61</t>
+          <t>37,58; 67,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,67; 71,18</t>
+          <t>42,58; 71,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,9; 72,76</t>
+          <t>42,59; 70,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55,19; 75,49</t>
+          <t>54,37; 74,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>41,81; 59,18</t>
+          <t>41,83; 58,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38,42; 58,15</t>
+          <t>38,66; 58,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54,43; 71,78</t>
+          <t>53,38; 71,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,5; 68,98</t>
+          <t>53,21; 68,56</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>53,28; 70,9</t>
+          <t>54,18; 72,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,55; 56,57</t>
+          <t>27,93; 56,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,71; 54,52</t>
+          <t>20,88; 53,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63,2; 85,82</t>
+          <t>63,82; 85,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,28; 76,77</t>
+          <t>50,41; 78,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,42; 73,58</t>
+          <t>36,34; 74,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,09; 75,51</t>
+          <t>30,69; 72,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,4; 69,29</t>
+          <t>36,21; 60,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54,68; 70,31</t>
+          <t>55,37; 71,08</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35,42; 59,63</t>
+          <t>36,32; 60,72</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30,59; 56,83</t>
+          <t>31,07; 56,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,42; 72,86</t>
+          <t>53,96; 70,38</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47,09; 56,66</t>
+          <t>47,51; 57,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49,14; 60,34</t>
+          <t>48,93; 61,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54,09; 65,21</t>
+          <t>54,02; 65,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55,66; 66,98</t>
+          <t>57,69; 68,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,96; 58,31</t>
+          <t>44,66; 58,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,95; 58,72</t>
+          <t>44,7; 58,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,93; 73,49</t>
+          <t>60,78; 73,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>59,7; 75,66</t>
+          <t>56,39; 65,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48,28; 55,92</t>
+          <t>48,48; 56,12</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49,26; 58,71</t>
+          <t>49,01; 58,39</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58,47; 66,71</t>
+          <t>58,22; 66,58</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>59,13; 68,85</t>
+          <t>58,06; 65,58</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>17472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26980</t>
+          <t>30399</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21655; 33892</t>
+          <t>22293; 34916</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15963; 29375</t>
+          <t>16493; 28970</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16585; 31667</t>
+          <t>14979; 31839</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8210; 18677</t>
+          <t>12344; 21407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9791; 20979</t>
+          <t>8985; 20343</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12825; 23115</t>
+          <t>12428; 23046</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21567; 33437</t>
+          <t>21778; 33545</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8498; 15165</t>
+          <t>9236; 15028</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34555; 51560</t>
+          <t>34133; 51486</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33363; 49346</t>
+          <t>31867; 49091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42192; 62099</t>
+          <t>42795; 63099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20906; 32480</t>
+          <t>23984; 35153</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26388</t>
+          <t>28430</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50197</t>
+          <t>53324</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27520; 46139</t>
+          <t>26272; 44954</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29053; 44022</t>
+          <t>28894; 43567</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53355; 69119</t>
+          <t>53977; 69183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18291; 35173</t>
+          <t>19502; 36385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13678; 24314</t>
+          <t>12864; 24232</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7827; 19757</t>
+          <t>8076; 19649</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27038; 38054</t>
+          <t>27369; 38537</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17984; 29902</t>
+          <t>18627; 30688</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45020; 65942</t>
+          <t>43959; 66313</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39647; 59087</t>
+          <t>39353; 59322</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85263; 105120</t>
+          <t>85657; 105210</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40196; 61072</t>
+          <t>42538; 62769</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>25767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>26045</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51048</t>
+          <t>51812</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13659; 25814</t>
+          <t>13773; 25331</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9790; 19507</t>
+          <t>10777; 20429</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13513; 20319</t>
+          <t>13324; 20329</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18491; 31810</t>
+          <t>18774; 31580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4834; 13734</t>
+          <t>4856; 13731</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4022; 12565</t>
+          <t>3836; 12628</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4005; 10788</t>
+          <t>3994; 10818</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20182; 31252</t>
+          <t>20361; 31070</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20965; 36253</t>
+          <t>21550; 35986</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17115; 30226</t>
+          <t>17594; 30632</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19920; 29559</t>
+          <t>20320; 29560</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42571; 59358</t>
+          <t>43309; 60250</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>70554</t>
+          <t>42636</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>101402</t>
+          <t>82625</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17455; 32603</t>
+          <t>16761; 32014</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15989; 30373</t>
+          <t>15791; 29832</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16171; 26752</t>
+          <t>15991; 27157</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23758; 36061</t>
+          <t>29793; 47426</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5176; 14268</t>
+          <t>5035; 14363</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10253; 20859</t>
+          <t>10279; 20860</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13567; 24402</t>
+          <t>14015; 24441</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60957; 77496</t>
+          <t>36402; 47232</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25371; 43034</t>
+          <t>24352; 43632</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29573; 47787</t>
+          <t>29874; 46672</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34155; 48947</t>
+          <t>34571; 49219</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88646; 113407</t>
+          <t>72278; 91496</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>16610</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4518; 13860</t>
+          <t>4397; 14019</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10507; 16169</t>
+          <t>10200; 16169</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4425; 12353</t>
+          <t>4183; 12458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4966; 11855</t>
+          <t>6399; 14554</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4005</t>
+          <t>0; 4008</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3540; 10723</t>
+          <t>3701; 10661</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1856; 5771</t>
+          <t>1943; 5771</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3020; 7273</t>
+          <t>3646; 8659</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5322; 15629</t>
+          <t>5724; 15623</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16370; 25399</t>
+          <t>16404; 25111</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8556; 17617</t>
+          <t>8067; 17499</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9279; 17576</t>
+          <t>11719; 21860</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36842</t>
+          <t>38769</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10526; 23692</t>
+          <t>10515; 23774</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17483; 30530</t>
+          <t>17549; 30542</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3820; 12865</t>
+          <t>3965; 13207</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14138; 24040</t>
+          <t>15846; 25588</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2776; 9889</t>
+          <t>2688; 9951</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>986; 8000</t>
+          <t>977; 7284</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3294; 7427</t>
+          <t>4292; 7427</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12622; 21534</t>
+          <t>13013; 21703</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16519; 30343</t>
+          <t>15966; 31284</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21548; 36881</t>
+          <t>21503; 36753</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9066; 19780</t>
+          <t>9235; 20175</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29593; 43206</t>
+          <t>31472; 44898</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41454</t>
+          <t>50106</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>46589</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88043</t>
+          <t>102568</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33071; 52900</t>
+          <t>34002; 54383</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14518; 29822</t>
+          <t>14725; 29535</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42028; 59941</t>
+          <t>42367; 59666</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32718; 49725</t>
+          <t>40181; 60609</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16480; 29433</t>
+          <t>16360; 29585</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19327; 33012</t>
+          <t>19748; 33301</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25001; 40516</t>
+          <t>23713; 39212</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>38920; 53239</t>
+          <t>43883; 59792</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>55180; 78108</t>
+          <t>55203; 77148</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38377; 58084</t>
+          <t>38620; 58769</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72954; 96196</t>
+          <t>71543; 95377</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>75440; 99126</t>
+          <t>88634; 114202</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42975</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>29258</t>
+          <t>27731</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>72233</t>
+          <t>77940</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>58026; 77224</t>
+          <t>59009; 78789</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12713; 26106</t>
+          <t>12890; 26287</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8921; 21411</t>
+          <t>8200; 21060</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35869; 48708</t>
+          <t>42537; 57141</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>25031; 38223</t>
+          <t>25097; 39307</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11171; 22568</t>
+          <t>11146; 22841</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6439; 16160</t>
+          <t>6567; 15489</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>22102; 37906</t>
+          <t>20815; 34925</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>86779; 111576</t>
+          <t>87873; 112798</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27213; 45807</t>
+          <t>27899; 46647</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18558; 34482</t>
+          <t>18852; 34134</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>61778; 81212</t>
+          <t>66981; 87366</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>208774</t>
+          <t>243557</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>231260</t>
+          <t>210491</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>440034</t>
+          <t>454048</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>222390; 267606</t>
+          <t>224382; 270196</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>159921; 196372</t>
+          <t>159251; 199040</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>189315; 228223</t>
+          <t>189080; 228492</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>188962; 227403</t>
+          <t>222094; 262984</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>98975; 128347</t>
+          <t>98303; 128383</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96046; 125458</t>
+          <t>95508; 124256</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>131790; 158949</t>
+          <t>131465; 158442</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>211471; 267993</t>
+          <t>194730; 226579</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>334291; 387206</t>
+          <t>335689; 388595</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>265561; 316514</t>
+          <t>264213; 314778</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>331123; 377794</t>
+          <t>329707; 377060</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>410195; 477653</t>
+          <t>424005; 478967</t>
         </is>
       </c>
     </row>
